--- a/ASTquizApp/qBanks/DRS.xlsx
+++ b/ASTquizApp/qBanks/DRS.xlsx
@@ -1,15 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programDo\vs\ASTquizApp\ASTquizApp\qBanks\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF7B3F83-4D7D-437E-A7F8-E5B4FC1E855D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$51</definedName>
@@ -19,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="164" count="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="164">
   <si>
     <t>Answer</t>
   </si>
@@ -524,51 +528,47 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="49" formatCode="@"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="8">
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="Arial"/>
-      <sz val="12"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -612,15 +612,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -628,19 +624,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -652,9 +646,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -663,15 +657,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -680,9 +670,29 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -723,35 +733,23 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16" count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -789,7 +787,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -823,6 +821,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -857,9 +856,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -965,7 +965,7 @@
             <a:camera prst="orthographicFront">
               <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
+            <a:lightRig rig="threePt" dir="t">
               <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
@@ -1032,28 +1032,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P51"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O51"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" hidden="1" customWidth="1" width="18.0" style="0"/>
-    <col min="2" max="2" hidden="1" customWidth="1" bestFit="1" width="18.285156" style="0"/>
-    <col min="3" max="3" hidden="1" customWidth="1" bestFit="1" width="6.7109375" style="0"/>
-    <col min="4" max="4" hidden="1" customWidth="1" bestFit="1" width="16.425781" style="0"/>
-    <col min="5" max="5" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="6" max="6" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="7" max="7" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="8" max="8" customWidth="1" width="64.71094" style="1"/>
-    <col min="9" max="9" customWidth="1" bestFit="1" width="21.140625" style="0"/>
-    <col min="10" max="10" customWidth="1" width="11.855469" style="0"/>
-    <col min="11" max="11" customWidth="1" width="13.425781" style="0"/>
-    <col min="12" max="12" customWidth="1" width="12.285156" style="0"/>
-    <col min="13" max="13" customWidth="1" width="9.855469" style="0"/>
-    <col min="14" max="14" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="15" max="15" hidden="1" customWidth="1" bestFit="1" width="18.710938" style="0"/>
+    <col min="1" max="1" width="18" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="64.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" customWidth="1"/>
+    <col min="13" max="13" width="9.85546875" customWidth="1"/>
+    <col min="14" max="14" width="10" hidden="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" hidden="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="8:8" s="2" ht="18.75" customFormat="1">
+    <row r="1" spans="1:15" s="2" customFormat="1" ht="18.75">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
@@ -1100,7 +1099,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="8:8" ht="60.0">
+    <row r="2" spans="1:15" ht="60">
       <c r="A2" s="5" t="s">
         <v>143</v>
       </c>
@@ -1108,7 +1107,7 @@
         <v>142</v>
       </c>
       <c r="C2" s="6">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>15</v>
@@ -1117,7 +1116,7 @@
         <v>21</v>
       </c>
       <c r="F2" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>109</v>
@@ -1141,13 +1140,13 @@
         <v>21</v>
       </c>
       <c r="N2" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O2" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="3" spans="8:8" ht="60.0">
+    <row r="3" spans="1:15" ht="60">
       <c r="A3" s="5" t="s">
         <v>143</v>
       </c>
@@ -1155,7 +1154,7 @@
         <v>142</v>
       </c>
       <c r="C3" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>15</v>
@@ -1164,7 +1163,7 @@
         <v>30</v>
       </c>
       <c r="F3" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>109</v>
@@ -1188,13 +1187,13 @@
         <v>27</v>
       </c>
       <c r="N3" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O3" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="8:8" ht="60.0">
+    <row r="4" spans="1:15" ht="60">
       <c r="A4" s="5" t="s">
         <v>143</v>
       </c>
@@ -1202,7 +1201,7 @@
         <v>142</v>
       </c>
       <c r="C4" s="6">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>15</v>
@@ -1211,7 +1210,7 @@
         <v>38</v>
       </c>
       <c r="F4" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>109</v>
@@ -1235,13 +1234,13 @@
         <v>30</v>
       </c>
       <c r="N4" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O4" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="5" spans="8:8" ht="60.0">
+    <row r="5" spans="1:15" ht="60">
       <c r="A5" s="5" t="s">
         <v>143</v>
       </c>
@@ -1249,7 +1248,7 @@
         <v>142</v>
       </c>
       <c r="C5" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>15</v>
@@ -1258,7 +1257,7 @@
         <v>30</v>
       </c>
       <c r="F5" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>104</v>
@@ -1278,13 +1277,13 @@
         <v>21</v>
       </c>
       <c r="N5" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O5" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="8:8" ht="60.0">
+    <row r="6" spans="1:15" ht="60">
       <c r="A6" s="5" t="s">
         <v>143</v>
       </c>
@@ -1292,7 +1291,7 @@
         <v>142</v>
       </c>
       <c r="C6" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>15</v>
@@ -1301,7 +1300,7 @@
         <v>38</v>
       </c>
       <c r="F6" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>109</v>
@@ -1325,13 +1324,13 @@
         <v>30</v>
       </c>
       <c r="N6" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O6" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="7" spans="8:8" ht="60.0">
+    <row r="7" spans="1:15" ht="60">
       <c r="A7" s="5" t="s">
         <v>143</v>
       </c>
@@ -1339,7 +1338,7 @@
         <v>142</v>
       </c>
       <c r="C7" s="6">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>15</v>
@@ -1348,7 +1347,7 @@
         <v>30</v>
       </c>
       <c r="F7" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>109</v>
@@ -1372,13 +1371,13 @@
         <v>38</v>
       </c>
       <c r="N7" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O7" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="8" spans="8:8" ht="60.0">
+    <row r="8" spans="1:15" ht="60">
       <c r="A8" s="5" t="s">
         <v>143</v>
       </c>
@@ -1386,7 +1385,7 @@
         <v>142</v>
       </c>
       <c r="C8" s="6">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>15</v>
@@ -1395,7 +1394,7 @@
         <v>21</v>
       </c>
       <c r="F8" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>109</v>
@@ -1419,13 +1418,13 @@
         <v>27</v>
       </c>
       <c r="N8" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O8" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="9" spans="8:8" ht="60.0">
+    <row r="9" spans="1:15" ht="60">
       <c r="A9" s="5" t="s">
         <v>143</v>
       </c>
@@ -1433,7 +1432,7 @@
         <v>142</v>
       </c>
       <c r="C9" s="6">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>15</v>
@@ -1442,7 +1441,7 @@
         <v>38</v>
       </c>
       <c r="F9" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>109</v>
@@ -1451,28 +1450,28 @@
         <v>40</v>
       </c>
       <c r="I9" s="8">
-        <v>1897.0</v>
+        <v>1897</v>
       </c>
       <c r="J9" s="8">
-        <v>1987.0</v>
+        <v>1987</v>
       </c>
       <c r="K9" s="8">
-        <v>1874.0</v>
+        <v>1874</v>
       </c>
       <c r="L9" s="8">
-        <v>1937.0</v>
+        <v>1937</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>21</v>
       </c>
       <c r="N9" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O9" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="8:8" ht="60.0">
+    <row r="10" spans="1:15" ht="60">
       <c r="A10" s="5" t="s">
         <v>143</v>
       </c>
@@ -1480,7 +1479,7 @@
         <v>142</v>
       </c>
       <c r="C10" s="6">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>15</v>
@@ -1489,7 +1488,7 @@
         <v>38</v>
       </c>
       <c r="F10" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>109</v>
@@ -1513,13 +1512,13 @@
         <v>30</v>
       </c>
       <c r="N10" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O10" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="11" spans="8:8" ht="60.0">
+    <row r="11" spans="1:15" ht="60">
       <c r="A11" s="5" t="s">
         <v>143</v>
       </c>
@@ -1527,7 +1526,7 @@
         <v>142</v>
       </c>
       <c r="C11" s="6">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>15</v>
@@ -1536,7 +1535,7 @@
         <v>30</v>
       </c>
       <c r="F11" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>109</v>
@@ -1560,13 +1559,13 @@
         <v>21</v>
       </c>
       <c r="N11" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O11" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="12" spans="8:8" ht="60.0">
+    <row r="12" spans="1:15" ht="60">
       <c r="A12" s="5" t="s">
         <v>143</v>
       </c>
@@ -1574,7 +1573,7 @@
         <v>142</v>
       </c>
       <c r="C12" s="6">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>15</v>
@@ -1583,7 +1582,7 @@
         <v>27</v>
       </c>
       <c r="F12" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>104</v>
@@ -1603,13 +1602,13 @@
         <v>21</v>
       </c>
       <c r="N12" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O12" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="13" spans="8:8" ht="60.0">
+    <row r="13" spans="1:15" ht="60">
       <c r="A13" s="5" t="s">
         <v>143</v>
       </c>
@@ -1617,7 +1616,7 @@
         <v>142</v>
       </c>
       <c r="C13" s="6">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>15</v>
@@ -1626,7 +1625,7 @@
         <v>38</v>
       </c>
       <c r="F13" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>109</v>
@@ -1650,13 +1649,13 @@
         <v>27</v>
       </c>
       <c r="N13" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O13" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="14" spans="8:8" ht="60.0">
+    <row r="14" spans="1:15" ht="60">
       <c r="A14" s="5" t="s">
         <v>143</v>
       </c>
@@ -1664,7 +1663,7 @@
         <v>142</v>
       </c>
       <c r="C14" s="6">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>15</v>
@@ -1673,7 +1672,7 @@
         <v>21</v>
       </c>
       <c r="F14" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>104</v>
@@ -1693,13 +1692,13 @@
         <v>30</v>
       </c>
       <c r="N14" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O14" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="15" spans="8:8" ht="60.0">
+    <row r="15" spans="1:15" ht="60">
       <c r="A15" s="5" t="s">
         <v>143</v>
       </c>
@@ -1707,7 +1706,7 @@
         <v>142</v>
       </c>
       <c r="C15" s="6">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>15</v>
@@ -1716,7 +1715,7 @@
         <v>30</v>
       </c>
       <c r="F15" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>109</v>
@@ -1740,13 +1739,13 @@
         <v>21</v>
       </c>
       <c r="N15" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O15" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="16" spans="8:8" ht="60.0">
+    <row r="16" spans="1:15" ht="60">
       <c r="A16" s="5" t="s">
         <v>143</v>
       </c>
@@ -1754,7 +1753,7 @@
         <v>142</v>
       </c>
       <c r="C16" s="6">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>15</v>
@@ -1763,7 +1762,7 @@
         <v>38</v>
       </c>
       <c r="F16" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>104</v>
@@ -1783,13 +1782,13 @@
         <v>21</v>
       </c>
       <c r="N16" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O16" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="17" spans="8:8" ht="60.0">
+    <row r="17" spans="1:15" ht="60">
       <c r="A17" s="5" t="s">
         <v>143</v>
       </c>
@@ -1797,7 +1796,7 @@
         <v>142</v>
       </c>
       <c r="C17" s="6">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>15</v>
@@ -1806,7 +1805,7 @@
         <v>27</v>
       </c>
       <c r="F17" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>109</v>
@@ -1815,28 +1814,28 @@
         <v>63</v>
       </c>
       <c r="I17" s="8">
-        <v>1906.0</v>
+        <v>1906</v>
       </c>
       <c r="J17" s="8">
-        <v>2006.0</v>
+        <v>2006</v>
       </c>
       <c r="K17" s="8">
-        <v>2010.0</v>
+        <v>2010</v>
       </c>
       <c r="L17" s="8">
-        <v>2008.0</v>
+        <v>2008</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>30</v>
       </c>
       <c r="N17" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O17" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="18" spans="8:8" ht="60.0">
+    <row r="18" spans="1:15" ht="60">
       <c r="A18" s="5" t="s">
         <v>143</v>
       </c>
@@ -1844,7 +1843,7 @@
         <v>142</v>
       </c>
       <c r="C18" s="6">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>15</v>
@@ -1853,7 +1852,7 @@
         <v>38</v>
       </c>
       <c r="F18" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>104</v>
@@ -1873,13 +1872,13 @@
         <v>21</v>
       </c>
       <c r="N18" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O18" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="19" spans="8:8" ht="60.0">
+    <row r="19" spans="1:15" ht="60">
       <c r="A19" s="5" t="s">
         <v>143</v>
       </c>
@@ -1887,7 +1886,7 @@
         <v>142</v>
       </c>
       <c r="C19" s="6">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>15</v>
@@ -1896,7 +1895,7 @@
         <v>21</v>
       </c>
       <c r="F19" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>109</v>
@@ -1920,13 +1919,13 @@
         <v>21</v>
       </c>
       <c r="N19" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O19" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="20" spans="8:8" ht="60.0">
+    <row r="20" spans="1:15" ht="60">
       <c r="A20" s="5" t="s">
         <v>143</v>
       </c>
@@ -1934,7 +1933,7 @@
         <v>142</v>
       </c>
       <c r="C20" s="6">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>15</v>
@@ -1943,7 +1942,7 @@
         <v>30</v>
       </c>
       <c r="F20" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>109</v>
@@ -1967,13 +1966,13 @@
         <v>27</v>
       </c>
       <c r="N20" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O20" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="21" spans="8:8" ht="60.0">
+    <row r="21" spans="1:15" ht="60">
       <c r="A21" s="5" t="s">
         <v>143</v>
       </c>
@@ -1981,7 +1980,7 @@
         <v>142</v>
       </c>
       <c r="C21" s="6">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>15</v>
@@ -1990,7 +1989,7 @@
         <v>27</v>
       </c>
       <c r="F21" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>109</v>
@@ -2014,13 +2013,13 @@
         <v>30</v>
       </c>
       <c r="N21" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O21" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="22" spans="8:8" ht="60.0">
+    <row r="22" spans="1:15" ht="60">
       <c r="A22" s="5" t="s">
         <v>143</v>
       </c>
@@ -2028,7 +2027,7 @@
         <v>142</v>
       </c>
       <c r="C22" s="6">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>15</v>
@@ -2037,7 +2036,7 @@
         <v>38</v>
       </c>
       <c r="F22" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>109</v>
@@ -2061,13 +2060,13 @@
         <v>27</v>
       </c>
       <c r="N22" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O22" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="23" spans="8:8" ht="75.0">
+    <row r="23" spans="1:15" ht="75">
       <c r="A23" s="5" t="s">
         <v>143</v>
       </c>
@@ -2075,7 +2074,7 @@
         <v>142</v>
       </c>
       <c r="C23" s="6">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>15</v>
@@ -2084,7 +2083,7 @@
         <v>30</v>
       </c>
       <c r="F23" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>109</v>
@@ -2108,13 +2107,13 @@
         <v>21</v>
       </c>
       <c r="N23" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O23" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="24" spans="8:8" ht="60.0">
+    <row r="24" spans="1:15" ht="60">
       <c r="A24" s="5" t="s">
         <v>143</v>
       </c>
@@ -2122,7 +2121,7 @@
         <v>142</v>
       </c>
       <c r="C24" s="6">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>15</v>
@@ -2131,7 +2130,7 @@
         <v>27</v>
       </c>
       <c r="F24" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>104</v>
@@ -2151,13 +2150,13 @@
         <v>30</v>
       </c>
       <c r="N24" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O24" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="8:8" ht="60.0">
+    <row r="25" spans="1:15" ht="60">
       <c r="A25" s="5" t="s">
         <v>143</v>
       </c>
@@ -2165,7 +2164,7 @@
         <v>142</v>
       </c>
       <c r="C25" s="6">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>15</v>
@@ -2174,7 +2173,7 @@
         <v>38</v>
       </c>
       <c r="F25" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>104</v>
@@ -2194,13 +2193,13 @@
         <v>30</v>
       </c>
       <c r="N25" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O25" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="26" spans="8:8" ht="60.0">
+    <row r="26" spans="1:15" ht="60">
       <c r="A26" s="5" t="s">
         <v>143</v>
       </c>
@@ -2208,7 +2207,7 @@
         <v>142</v>
       </c>
       <c r="C26" s="6">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>15</v>
@@ -2217,7 +2216,7 @@
         <v>30</v>
       </c>
       <c r="F26" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>104</v>
@@ -2237,13 +2236,13 @@
         <v>30</v>
       </c>
       <c r="N26" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O26" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="27" spans="8:8" ht="60.0">
+    <row r="27" spans="1:15" ht="60">
       <c r="A27" s="5" t="s">
         <v>143</v>
       </c>
@@ -2251,7 +2250,7 @@
         <v>142</v>
       </c>
       <c r="C27" s="6">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>15</v>
@@ -2260,7 +2259,7 @@
         <v>38</v>
       </c>
       <c r="F27" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>104</v>
@@ -2280,13 +2279,13 @@
         <v>21</v>
       </c>
       <c r="N27" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O27" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="28" spans="8:8" ht="60.0">
+    <row r="28" spans="1:15" ht="60">
       <c r="A28" s="5" t="s">
         <v>143</v>
       </c>
@@ -2294,7 +2293,7 @@
         <v>142</v>
       </c>
       <c r="C28" s="6">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>15</v>
@@ -2303,7 +2302,7 @@
         <v>27</v>
       </c>
       <c r="F28" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>109</v>
@@ -2327,13 +2326,13 @@
         <v>38</v>
       </c>
       <c r="N28" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O28" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="29" spans="8:8" ht="60.0">
+    <row r="29" spans="1:15" ht="60">
       <c r="A29" s="5" t="s">
         <v>143</v>
       </c>
@@ -2341,7 +2340,7 @@
         <v>142</v>
       </c>
       <c r="C29" s="6">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>15</v>
@@ -2350,7 +2349,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>104</v>
@@ -2370,13 +2369,13 @@
         <v>30</v>
       </c>
       <c r="N29" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O29" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="30" spans="8:8" ht="60.0">
+    <row r="30" spans="1:15" ht="60">
       <c r="A30" s="5" t="s">
         <v>143</v>
       </c>
@@ -2384,7 +2383,7 @@
         <v>142</v>
       </c>
       <c r="C30" s="6">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>15</v>
@@ -2393,7 +2392,7 @@
         <v>30</v>
       </c>
       <c r="F30" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>104</v>
@@ -2413,13 +2412,13 @@
         <v>21</v>
       </c>
       <c r="N30" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O30" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="31" spans="8:8" ht="60.0">
+    <row r="31" spans="1:15" ht="60">
       <c r="A31" s="5" t="s">
         <v>143</v>
       </c>
@@ -2427,7 +2426,7 @@
         <v>142</v>
       </c>
       <c r="C31" s="6">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>15</v>
@@ -2436,7 +2435,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>104</v>
@@ -2456,13 +2455,13 @@
         <v>21</v>
       </c>
       <c r="N31" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O31" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="32" spans="8:8" ht="60.0">
+    <row r="32" spans="1:15" ht="60">
       <c r="A32" s="5" t="s">
         <v>143</v>
       </c>
@@ -2470,7 +2469,7 @@
         <v>142</v>
       </c>
       <c r="C32" s="6">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>15</v>
@@ -2479,7 +2478,7 @@
         <v>38</v>
       </c>
       <c r="F32" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>104</v>
@@ -2499,13 +2498,13 @@
         <v>30</v>
       </c>
       <c r="N32" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O32" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="8:8" ht="60.0">
+    <row r="33" spans="1:15" ht="60">
       <c r="A33" s="5" t="s">
         <v>143</v>
       </c>
@@ -2513,7 +2512,7 @@
         <v>142</v>
       </c>
       <c r="C33" s="6">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>15</v>
@@ -2522,7 +2521,7 @@
         <v>30</v>
       </c>
       <c r="F33" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>104</v>
@@ -2542,13 +2541,13 @@
         <v>21</v>
       </c>
       <c r="N33" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O33" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="34" spans="8:8" ht="60.0">
+    <row r="34" spans="1:15" ht="60">
       <c r="A34" s="5" t="s">
         <v>143</v>
       </c>
@@ -2556,7 +2555,7 @@
         <v>142</v>
       </c>
       <c r="C34" s="6">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>15</v>
@@ -2565,7 +2564,7 @@
         <v>27</v>
       </c>
       <c r="F34" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>104</v>
@@ -2585,13 +2584,13 @@
         <v>21</v>
       </c>
       <c r="N34" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O34" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="35" spans="8:8" ht="60.0">
+    <row r="35" spans="1:15" ht="60">
       <c r="A35" s="5" t="s">
         <v>143</v>
       </c>
@@ -2599,7 +2598,7 @@
         <v>142</v>
       </c>
       <c r="C35" s="6">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>15</v>
@@ -2608,7 +2607,7 @@
         <v>21</v>
       </c>
       <c r="F35" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>109</v>
@@ -2617,10 +2616,10 @@
         <v>91</v>
       </c>
       <c r="I35" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K35" s="5" t="s">
         <v>92</v>
@@ -2632,13 +2631,13 @@
         <v>27</v>
       </c>
       <c r="N35" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O35" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="36" spans="8:8" ht="60.0">
+    <row r="36" spans="1:15" ht="60">
       <c r="A36" s="5" t="s">
         <v>143</v>
       </c>
@@ -2646,7 +2645,7 @@
         <v>142</v>
       </c>
       <c r="C36" s="6">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>15</v>
@@ -2655,7 +2654,7 @@
         <v>30</v>
       </c>
       <c r="F36" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>104</v>
@@ -2675,13 +2674,13 @@
         <v>21</v>
       </c>
       <c r="N36" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O36" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="37" spans="8:8" ht="75.0">
+    <row r="37" spans="1:15" ht="75">
       <c r="A37" s="5" t="s">
         <v>143</v>
       </c>
@@ -2689,7 +2688,7 @@
         <v>142</v>
       </c>
       <c r="C37" s="6">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>15</v>
@@ -2698,7 +2697,7 @@
         <v>27</v>
       </c>
       <c r="F37" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>109</v>
@@ -2722,13 +2721,13 @@
         <v>27</v>
       </c>
       <c r="N37" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O37" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="38" spans="8:8" ht="60.0">
+    <row r="38" spans="1:15" ht="60">
       <c r="A38" s="5" t="s">
         <v>143</v>
       </c>
@@ -2736,7 +2735,7 @@
         <v>142</v>
       </c>
       <c r="C38" s="6">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>15</v>
@@ -2745,7 +2744,7 @@
         <v>21</v>
       </c>
       <c r="F38" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>109</v>
@@ -2769,13 +2768,13 @@
         <v>38</v>
       </c>
       <c r="N38" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O38" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="39" spans="8:8" s="18" ht="60.0" customFormat="1">
+    <row r="39" spans="1:15" s="18" customFormat="1" ht="60">
       <c r="A39" s="5" t="s">
         <v>143</v>
       </c>
@@ -2783,7 +2782,7 @@
         <v>142</v>
       </c>
       <c r="C39" s="6">
-        <v>38.0</v>
+        <v>38</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>103</v>
@@ -2792,7 +2791,7 @@
         <v>21</v>
       </c>
       <c r="F39" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>104</v>
@@ -2812,13 +2811,13 @@
         <v>21</v>
       </c>
       <c r="N39" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O39" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="40" spans="8:8" s="18" ht="60.0" customFormat="1">
+    <row r="40" spans="1:15" s="18" customFormat="1" ht="60">
       <c r="A40" s="5" t="s">
         <v>143</v>
       </c>
@@ -2826,7 +2825,7 @@
         <v>142</v>
       </c>
       <c r="C40" s="6">
-        <v>39.0</v>
+        <v>39</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>103</v>
@@ -2835,7 +2834,7 @@
         <v>30</v>
       </c>
       <c r="F40" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>104</v>
@@ -2855,13 +2854,13 @@
         <v>21</v>
       </c>
       <c r="N40" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O40" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="8:8" s="18" ht="60.0" customFormat="1">
+    <row r="41" spans="1:15" s="18" customFormat="1" ht="60">
       <c r="A41" s="5" t="s">
         <v>143</v>
       </c>
@@ -2869,7 +2868,7 @@
         <v>142</v>
       </c>
       <c r="C41" s="6">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>108</v>
@@ -2878,7 +2877,7 @@
         <v>38</v>
       </c>
       <c r="F41" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>109</v>
@@ -2902,13 +2901,13 @@
         <v>30</v>
       </c>
       <c r="N41" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O41" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="42" spans="8:8" s="18" ht="60.0" customFormat="1">
+    <row r="42" spans="1:15" s="18" customFormat="1" ht="60">
       <c r="A42" s="5" t="s">
         <v>143</v>
       </c>
@@ -2916,7 +2915,7 @@
         <v>142</v>
       </c>
       <c r="C42" s="6">
-        <v>41.0</v>
+        <v>41</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>108</v>
@@ -2925,7 +2924,7 @@
         <v>30</v>
       </c>
       <c r="F42" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>109</v>
@@ -2949,13 +2948,13 @@
         <v>21</v>
       </c>
       <c r="N42" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O42" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="43" spans="8:8" s="18" ht="60.0" customFormat="1">
+    <row r="43" spans="1:15" s="18" customFormat="1" ht="60">
       <c r="A43" s="5" t="s">
         <v>143</v>
       </c>
@@ -2963,7 +2962,7 @@
         <v>142</v>
       </c>
       <c r="C43" s="6">
-        <v>42.0</v>
+        <v>42</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>120</v>
@@ -2972,7 +2971,7 @@
         <v>21</v>
       </c>
       <c r="F43" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>109</v>
@@ -2996,13 +2995,13 @@
         <v>38</v>
       </c>
       <c r="N43" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O43" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="8:8" s="18" ht="105.0" customFormat="1">
+    <row r="44" spans="1:15" s="18" customFormat="1" ht="105">
       <c r="A44" s="5" t="s">
         <v>143</v>
       </c>
@@ -3010,7 +3009,7 @@
         <v>142</v>
       </c>
       <c r="C44" s="6">
-        <v>43.0</v>
+        <v>43</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>120</v>
@@ -3019,7 +3018,7 @@
         <v>38</v>
       </c>
       <c r="F44" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>109</v>
@@ -3043,13 +3042,13 @@
         <v>27</v>
       </c>
       <c r="N44" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O44" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="45" spans="8:8" s="18" ht="60.0" customFormat="1">
+    <row r="45" spans="1:15" s="18" customFormat="1" ht="60">
       <c r="A45" s="5" t="s">
         <v>143</v>
       </c>
@@ -3057,7 +3056,7 @@
         <v>142</v>
       </c>
       <c r="C45" s="6">
-        <v>44.0</v>
+        <v>44</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>120</v>
@@ -3066,7 +3065,7 @@
         <v>30</v>
       </c>
       <c r="F45" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>104</v>
@@ -3086,13 +3085,13 @@
         <v>21</v>
       </c>
       <c r="N45" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O45" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="46" spans="8:8" s="18" ht="60.0" customFormat="1">
+    <row r="46" spans="1:15" s="18" customFormat="1" ht="60">
       <c r="A46" s="5" t="s">
         <v>143</v>
       </c>
@@ -3100,7 +3099,7 @@
         <v>142</v>
       </c>
       <c r="C46" s="6">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>120</v>
@@ -3109,7 +3108,7 @@
         <v>38</v>
       </c>
       <c r="F46" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>104</v>
@@ -3129,13 +3128,13 @@
         <v>21</v>
       </c>
       <c r="N46" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O46" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="47" spans="8:8" s="18" ht="60.0" customFormat="1">
+    <row r="47" spans="1:15" s="18" customFormat="1" ht="60">
       <c r="A47" s="5" t="s">
         <v>143</v>
       </c>
@@ -3143,7 +3142,7 @@
         <v>142</v>
       </c>
       <c r="C47" s="6">
-        <v>46.0</v>
+        <v>46</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>120</v>
@@ -3152,7 +3151,7 @@
         <v>27</v>
       </c>
       <c r="F47" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>109</v>
@@ -3176,13 +3175,13 @@
         <v>27</v>
       </c>
       <c r="N47" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O47" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="8:8" s="18" ht="60.0" customFormat="1">
+    <row r="48" spans="1:15" s="18" customFormat="1" ht="60">
       <c r="A48" s="5" t="s">
         <v>143</v>
       </c>
@@ -3190,7 +3189,7 @@
         <v>142</v>
       </c>
       <c r="C48" s="6">
-        <v>47.0</v>
+        <v>47</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>120</v>
@@ -3199,7 +3198,7 @@
         <v>38</v>
       </c>
       <c r="F48" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>109</v>
@@ -3223,13 +3222,13 @@
         <v>27</v>
       </c>
       <c r="N48" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O48" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="49" spans="8:8" s="20" ht="60.0" customFormat="1">
+    <row r="49" spans="1:15" s="20" customFormat="1" ht="60">
       <c r="A49" s="21" t="s">
         <v>154</v>
       </c>
@@ -3237,7 +3236,7 @@
         <v>142</v>
       </c>
       <c r="C49" s="6">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>155</v>
@@ -3246,7 +3245,7 @@
         <v>27</v>
       </c>
       <c r="F49" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>109</v>
@@ -3270,13 +3269,13 @@
         <v>21</v>
       </c>
       <c r="N49" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O49" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="50" spans="8:8" s="20" ht="60.0" customFormat="1">
+    <row r="50" spans="1:15" s="20" customFormat="1" ht="60">
       <c r="A50" s="21" t="s">
         <v>154</v>
       </c>
@@ -3284,7 +3283,7 @@
         <v>142</v>
       </c>
       <c r="C50" s="6">
-        <v>49.0</v>
+        <v>49</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>161</v>
@@ -3293,7 +3292,7 @@
         <v>30</v>
       </c>
       <c r="F50" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>104</v>
@@ -3313,13 +3312,13 @@
         <v>30</v>
       </c>
       <c r="N50" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O50" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="51" spans="8:8" s="20" ht="60.0" customFormat="1">
+    <row r="51" spans="1:15" s="20" customFormat="1" ht="60">
       <c r="A51" s="21" t="s">
         <v>154</v>
       </c>
@@ -3327,7 +3326,7 @@
         <v>142</v>
       </c>
       <c r="C51" s="6">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>161</v>
@@ -3336,7 +3335,7 @@
         <v>27</v>
       </c>
       <c r="F51" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>104</v>
@@ -3356,7 +3355,7 @@
         <v>21</v>
       </c>
       <c r="N51" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O51" s="5" t="s">
         <v>106</v>
@@ -3364,33 +3363,15 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H1">
-    <cfRule type="duplicateValues" priority="9" dxfId="0"/>
-    <cfRule type="duplicateValues" priority="5" dxfId="1"/>
-    <cfRule type="duplicateValues" priority="6" dxfId="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H29:H38">
-    <cfRule type="duplicateValues" priority="14" dxfId="3"/>
-    <cfRule type="duplicateValues" priority="15" dxfId="4"/>
-    <cfRule type="duplicateValues" priority="13" dxfId="5"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>